--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>幸运夺宝(一元购)</t>
+  </si>
+  <si>
+    <t>空袭</t>
+  </si>
+  <si>
+    <t>鸿运扑克</t>
+  </si>
+  <si>
+    <t>hillo</t>
+  </si>
+  <si>
+    <t>高低扑克</t>
   </si>
 </sst>
 </file>
@@ -1110,28 +1122,52 @@
         <v>7</v>
       </c>
       <c r="C5" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8">
+        <v>400400</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-    </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="9">
+        <v>400200</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="9">
+        <v>400500</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="9">
+        <v>400700</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="10"/>

--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -51,18 +51,6 @@
   </si>
   <si>
     <t>幸运夺宝(一元购)</t>
-  </si>
-  <si>
-    <t>空袭</t>
-  </si>
-  <si>
-    <t>鸿运扑克</t>
-  </si>
-  <si>
-    <t>hillo</t>
-  </si>
-  <si>
-    <t>高低扑克</t>
   </si>
 </sst>
 </file>
@@ -1126,48 +1114,24 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="8">
-        <v>400400</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="9">
-        <v>400200</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="9">
-        <v>400500</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="9">
-        <v>400700</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="10"/>

--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="MiniGameList" sheetId="1" r:id="rId1"/>
@@ -1110,7 +1110,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">

--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MiniGameList" sheetId="1" r:id="rId1"/>
@@ -1110,7 +1110,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
